--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run10/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run10/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,784 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8866,0.0569,0.0237,0.0330</t>
-  </si>
-  <si>
-    <t>0.0078,0.0104,0.0018,0.9932</t>
-  </si>
-  <si>
-    <t>0.7402,0.0266,0.0093,0.2520</t>
-  </si>
-  <si>
-    <t>0.0129,0.0044,0.0009,0.9934</t>
-  </si>
-  <si>
-    <t>0.9961,0.0006,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.9896,0.0019,0.0004,0.0032</t>
-  </si>
-  <si>
-    <t>0.9859,0.0091,0.0019,0.0012</t>
-  </si>
-  <si>
-    <t>0.9918,0.0037,0.0006,0.0012</t>
-  </si>
-  <si>
-    <t>0.9905,0.0051,0.0005,0.0012</t>
-  </si>
-  <si>
-    <t>0.9941,0.0024,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9922,0.0034,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9972,0.0007,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.7387,0.0805,0.2069,0.0177</t>
-  </si>
-  <si>
-    <t>0.2768,0.0198,0.8200,0.0026</t>
-  </si>
-  <si>
-    <t>0.3445,0.0228,0.7508,0.0018</t>
-  </si>
-  <si>
-    <t>0.3953,0.0360,0.5505,0.0612</t>
-  </si>
-  <si>
-    <t>0.5851,0.1436,0.3222,0.0111</t>
-  </si>
-  <si>
-    <t>0.0005,0.9984,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0113,0.9838,0.0033,0.0005</t>
-  </si>
-  <si>
-    <t>0.5022,0.6178,0.0064,0.0007</t>
-  </si>
-  <si>
-    <t>0.0069,0.9891,0.0016,0.0008</t>
-  </si>
-  <si>
-    <t>0.0024,0.9944,0.0017,0.0004</t>
-  </si>
-  <si>
-    <t>0.5568,0.0264,0.3559,0.0834</t>
-  </si>
-  <si>
-    <t>0.4875,0.0394,0.4727,0.0285</t>
-  </si>
-  <si>
-    <t>0.0752,0.0248,0.8913,0.0203</t>
-  </si>
-  <si>
-    <t>0.4632,0.0223,0.5281,0.0422</t>
-  </si>
-  <si>
-    <t>0.0313,0.0023,0.9780,0.0015</t>
-  </si>
-  <si>
-    <t>0.1348,0.0200,0.8654,0.0128</t>
-  </si>
-  <si>
-    <t>0.0266,0.0025,0.9782,0.0022</t>
-  </si>
-  <si>
-    <t>0.7401,0.3461,0.0096,0.0010</t>
-  </si>
-  <si>
-    <t>0.5737,0.3180,0.2210,0.0145</t>
-  </si>
-  <si>
-    <t>0.0061,0.0082,0.9804,0.0144</t>
-  </si>
-  <si>
-    <t>0.0016,0.9880,0.0452,0.0002</t>
-  </si>
-  <si>
-    <t>0.7532,0.2809,0.0305,0.0087</t>
-  </si>
-  <si>
-    <t>0.7035,0.1774,0.1094,0.0047</t>
-  </si>
-  <si>
-    <t>0.5915,0.5276,0.0070,0.0030</t>
-  </si>
-  <si>
-    <t>0.0123,0.9578,0.1438,0.0020</t>
-  </si>
-  <si>
-    <t>0.0223,0.8882,0.0723,0.0579</t>
-  </si>
-  <si>
-    <t>0.0979,0.2331,0.8004,0.0530</t>
-  </si>
-  <si>
-    <t>0.0890,0.1165,0.7993,0.0556</t>
-  </si>
-  <si>
-    <t>0.1310,0.0722,0.7630,0.1075</t>
-  </si>
-  <si>
-    <t>0.0379,0.0893,0.9268,0.0011</t>
-  </si>
-  <si>
-    <t>0.0061,0.9732,0.0474,0.0007</t>
-  </si>
-  <si>
-    <t>0.0280,0.0715,0.9583,0.0027</t>
-  </si>
-  <si>
-    <t>0.5304,0.0871,0.0047,0.4196</t>
-  </si>
-  <si>
-    <t>0.0101,0.9748,0.0109,0.0025</t>
-  </si>
-  <si>
-    <t>0.0073,0.9835,0.0150,0.0001</t>
-  </si>
-  <si>
-    <t>0.0027,0.9884,0.0157,0.0008</t>
-  </si>
-  <si>
-    <t>0.0296,0.1843,0.9046,0.0051</t>
-  </si>
-  <si>
-    <t>0.0027,0.6850,0.9399,0.0003</t>
-  </si>
-  <si>
-    <t>0.1859,0.0220,0.8483,0.0063</t>
-  </si>
-  <si>
-    <t>0.1008,0.0054,0.9428,0.0008</t>
-  </si>
-  <si>
-    <t>0.0185,0.0553,0.9672,0.0012</t>
-  </si>
-  <si>
-    <t>0.0139,0.0046,0.9822,0.0013</t>
-  </si>
-  <si>
-    <t>0.9847,0.0155,0.0019,0.0007</t>
-  </si>
-  <si>
-    <t>0.9642,0.0207,0.0045,0.0044</t>
-  </si>
-  <si>
-    <t>0.9959,0.0009,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.0047,0.0512,0.9720,0.0189</t>
-  </si>
-  <si>
-    <t>0.9838,0.0038,0.0003,0.0046</t>
-  </si>
-  <si>
-    <t>0.9932,0.0016,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9362,0.1098,0.0016,0.0011</t>
-  </si>
-  <si>
-    <t>0.0041,0.7642,0.9004,0.0009</t>
-  </si>
-  <si>
-    <t>0.0064,0.0463,0.9600,0.0254</t>
-  </si>
-  <si>
-    <t>0.0108,0.0209,0.9725,0.0112</t>
-  </si>
-  <si>
-    <t>0.0019,0.7301,0.9620,0.0003</t>
-  </si>
-  <si>
-    <t>0.0064,0.0049,0.9898,0.0013</t>
-  </si>
-  <si>
-    <t>0.0231,0.9559,0.0312,0.0009</t>
-  </si>
-  <si>
-    <t>0.0018,0.9963,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.3097,0.0142,0.7863,0.0060</t>
-  </si>
-  <si>
-    <t>0.4372,0.3687,0.3819,0.0235</t>
-  </si>
-  <si>
-    <t>0.0176,0.0339,0.9754,0.0014</t>
-  </si>
-  <si>
-    <t>0.0075,0.9437,0.4326,0.0005</t>
-  </si>
-  <si>
-    <t>0.0014,0.9806,0.4754,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.9910,0.0365,0.0006</t>
-  </si>
-  <si>
-    <t>0.0008,0.9785,0.7121,0.0002</t>
-  </si>
-  <si>
-    <t>0.0498,0.0061,0.0353,0.9439</t>
-  </si>
-  <si>
-    <t>0.0008,0.0015,0.0009,0.9989</t>
-  </si>
-  <si>
-    <t>0.0061,0.0018,0.0003,0.9969</t>
-  </si>
-  <si>
-    <t>0.0111,0.0347,0.0018,0.9897</t>
-  </si>
-  <si>
-    <t>0.0019,0.0118,0.0013,0.9971</t>
-  </si>
-  <si>
-    <t>0.0008,0.0029,0.0007,0.9988</t>
-  </si>
-  <si>
-    <t>0.0025,0.9478,0.7251,0.0005</t>
-  </si>
-  <si>
-    <t>0.0019,0.7252,0.9377,0.0002</t>
-  </si>
-  <si>
-    <t>0.0234,0.6553,0.7922,0.0075</t>
-  </si>
-  <si>
-    <t>0.0037,0.9073,0.5480,0.0053</t>
-  </si>
-  <si>
-    <t>0.0028,0.9157,0.8077,0.0005</t>
-  </si>
-  <si>
-    <t>0.0017,0.9376,0.8048,0.0002</t>
-  </si>
-  <si>
-    <t>0.9914,0.0037,0.0009,0.0012</t>
-  </si>
-  <si>
-    <t>0.9784,0.0349,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9913,0.0045,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.9961,0.0016,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9754,0.0266,0.0025,0.0013</t>
-  </si>
-  <si>
-    <t>0.9938,0.0015,0.0002,0.0013</t>
-  </si>
-  <si>
-    <t>0.9926,0.0050,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9792,0.0201,0.0013,0.0009</t>
-  </si>
-  <si>
-    <t>0.9935,0.0051,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9943,0.0023,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9900,0.0040,0.0005,0.0017</t>
-  </si>
-  <si>
-    <t>0.9980,0.0006,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9957,0.0016,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9944,0.0011,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.9876,0.0021,0.0003,0.0039</t>
-  </si>
-  <si>
-    <t>0.9947,0.0012,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.0944,0.0110,0.9168,0.0184</t>
-  </si>
-  <si>
-    <t>0.0519,0.0049,0.9577,0.0016</t>
-  </si>
-  <si>
-    <t>0.7393,0.0658,0.1641,0.0994</t>
-  </si>
-  <si>
-    <t>0.0996,0.0040,0.9355,0.0030</t>
-  </si>
-  <si>
-    <t>0.0054,0.9892,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.0090,0.9871,0.0062,0.0002</t>
-  </si>
-  <si>
-    <t>0.0352,0.9556,0.0028,0.0029</t>
-  </si>
-  <si>
-    <t>0.0430,0.9577,0.0029,0.0019</t>
-  </si>
-  <si>
-    <t>0.0054,0.9898,0.0018,0.0004</t>
-  </si>
-  <si>
-    <t>0.0019,0.9945,0.0028,0.0003</t>
-  </si>
-  <si>
-    <t>0.4009,0.7037,0.0026,0.0019</t>
-  </si>
-  <si>
-    <t>0.8295,0.0624,0.0629,0.0485</t>
-  </si>
-  <si>
-    <t>0.3851,0.0097,0.7610,0.0020</t>
-  </si>
-  <si>
-    <t>0.4566,0.3115,0.2874,0.1745</t>
-  </si>
-  <si>
-    <t>0.4965,0.1266,0.4766,0.0875</t>
-  </si>
-  <si>
-    <t>0.2537,0.0344,0.0175,0.7577</t>
-  </si>
-  <si>
-    <t>0.0016,0.9924,0.0048,0.0008</t>
-  </si>
-  <si>
-    <t>0.0017,0.9787,0.0042,0.0310</t>
-  </si>
-  <si>
-    <t>0.0116,0.9682,0.0148,0.0089</t>
-  </si>
-  <si>
-    <t>0.0002,0.9769,0.8738,0.0001</t>
-  </si>
-  <si>
-    <t>0.0064,0.9792,0.1010,0.0002</t>
-  </si>
-  <si>
-    <t>0.5580,0.5568,0.0092,0.0003</t>
-  </si>
-  <si>
-    <t>0.8767,0.1819,0.0072,0.0013</t>
-  </si>
-  <si>
-    <t>0.9913,0.0027,0.0007,0.0017</t>
-  </si>
-  <si>
-    <t>0.9896,0.0026,0.0005,0.0024</t>
-  </si>
-  <si>
-    <t>0.9819,0.0022,0.0003,0.0077</t>
-  </si>
-  <si>
-    <t>0.9804,0.0047,0.0019,0.0049</t>
-  </si>
-  <si>
-    <t>0.9937,0.0014,0.0004,0.0013</t>
-  </si>
-  <si>
-    <t>0.9670,0.0271,0.0040,0.0038</t>
-  </si>
-  <si>
-    <t>0.9762,0.0007,0.0001,0.0162</t>
-  </si>
-  <si>
-    <t>0.9920,0.0012,0.0003,0.0023</t>
-  </si>
-  <si>
-    <t>0.0090,0.1527,0.9600,0.0016</t>
-  </si>
-  <si>
-    <t>0.0018,0.7829,0.9179,0.0002</t>
-  </si>
-  <si>
-    <t>0.0062,0.8685,0.6877,0.0022</t>
-  </si>
-  <si>
-    <t>0.0273,0.1291,0.8856,0.0049</t>
-  </si>
-  <si>
-    <t>0.7797,0.0411,0.0902,0.0707</t>
-  </si>
-  <si>
-    <t>0.7885,0.0779,0.1185,0.0282</t>
-  </si>
-  <si>
-    <t>0.6959,0.0048,0.2358,0.0238</t>
-  </si>
-  <si>
-    <t>0.6483,0.1543,0.1345,0.0584</t>
-  </si>
-  <si>
-    <t>0.0112,0.0040,0.0006,0.9946</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0023,0.9994</t>
-  </si>
-  <si>
-    <t>0.0008,0.1164,0.0024,0.9954</t>
-  </si>
-  <si>
-    <t>0.0031,0.0015,0.0029,0.9966</t>
-  </si>
-  <si>
-    <t>0.0022,0.8434,0.7410,0.0045</t>
-  </si>
-  <si>
-    <t>0.9861,0.0044,0.0013,0.0017</t>
-  </si>
-  <si>
-    <t>0.8978,0.1019,0.0157,0.0068</t>
-  </si>
-  <si>
-    <t>0.9868,0.0014,0.0004,0.0064</t>
-  </si>
-  <si>
-    <t>0.7891,0.3240,0.0020,0.0016</t>
-  </si>
-  <si>
-    <t>0.9594,0.0084,0.0086,0.0094</t>
-  </si>
-  <si>
-    <t>0.7391,0.0374,0.0176,0.1841</t>
-  </si>
-  <si>
-    <t>0.9818,0.0040,0.0009,0.0053</t>
-  </si>
-  <si>
-    <t>0.0006,0.0744,0.9862,0.0036</t>
-  </si>
-  <si>
-    <t>0.7500,0.0010,0.0014,0.4096</t>
-  </si>
-  <si>
-    <t>0.9554,0.0135,0.0039,0.0142</t>
-  </si>
-  <si>
-    <t>0.3952,0.6617,0.0430,0.0093</t>
-  </si>
-  <si>
-    <t>0.9030,0.0659,0.0093,0.0120</t>
-  </si>
-  <si>
-    <t>0.8385,0.0647,0.1155,0.0062</t>
-  </si>
-  <si>
-    <t>0.2005,0.7581,0.0548,0.0313</t>
-  </si>
-  <si>
-    <t>0.3095,0.7532,0.0102,0.0014</t>
-  </si>
-  <si>
-    <t>0.7191,0.3672,0.0105,0.0017</t>
-  </si>
-  <si>
-    <t>0.9929,0.0013,0.0001,0.0014</t>
-  </si>
-  <si>
-    <t>0.9868,0.0054,0.0005,0.0026</t>
-  </si>
-  <si>
-    <t>0.9940,0.0031,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9867,0.0019,0.0009,0.0053</t>
-  </si>
-  <si>
-    <t>0.9844,0.0084,0.0021,0.0013</t>
-  </si>
-  <si>
-    <t>0.9841,0.0051,0.0017,0.0025</t>
-  </si>
-  <si>
-    <t>0.9921,0.0022,0.0003,0.0013</t>
-  </si>
-  <si>
-    <t>0.9786,0.0118,0.0025,0.0033</t>
-  </si>
-  <si>
-    <t>0.5583,0.5433,0.0097,0.0035</t>
-  </si>
-  <si>
-    <t>0.2292,0.8258,0.0092,0.0007</t>
-  </si>
-  <si>
-    <t>0.2710,0.8213,0.0023,0.0009</t>
-  </si>
-  <si>
-    <t>0.3514,0.4351,0.3497,0.0156</t>
-  </si>
-  <si>
-    <t>0.6619,0.5372,0.0019,0.0009</t>
-  </si>
-  <si>
-    <t>0.8907,0.1179,0.0112,0.0072</t>
-  </si>
-  <si>
-    <t>0.9846,0.0084,0.0011,0.0014</t>
-  </si>
-  <si>
-    <t>0.5548,0.6049,0.0045,0.0009</t>
-  </si>
-  <si>
-    <t>0.0057,0.0111,0.9913,0.0010</t>
-  </si>
-  <si>
-    <t>0.8978,0.1262,0.0148,0.0020</t>
-  </si>
-  <si>
-    <t>0.0055,0.0031,0.9927,0.0016</t>
-  </si>
-  <si>
-    <t>0.0190,0.0813,0.9220,0.0209</t>
-  </si>
-  <si>
-    <t>0.3029,0.1164,0.6682,0.0382</t>
-  </si>
-  <si>
-    <t>0.0198,0.1694,0.9483,0.0018</t>
-  </si>
-  <si>
-    <t>0.0599,0.0084,0.9505,0.0027</t>
-  </si>
-  <si>
-    <t>0.0620,0.0011,0.9700,0.0004</t>
-  </si>
-  <si>
-    <t>0.0131,0.0164,0.9822,0.0006</t>
-  </si>
-  <si>
-    <t>0.5476,0.0835,0.4215,0.0139</t>
-  </si>
-  <si>
-    <t>0.6025,0.1820,0.2071,0.0968</t>
-  </si>
-  <si>
-    <t>0.1169,0.8164,0.0716,0.0071</t>
-  </si>
-  <si>
-    <t>0.1402,0.4643,0.2754,0.0025</t>
-  </si>
-  <si>
-    <t>0.6185,0.0519,0.3545,0.0010</t>
-  </si>
-  <si>
-    <t>0.4634,0.0620,0.5571,0.0079</t>
-  </si>
-  <si>
-    <t>0.7484,0.0340,0.1944,0.0324</t>
-  </si>
-  <si>
-    <t>0.3674,0.4594,0.2645,0.0283</t>
-  </si>
-  <si>
-    <t>0.2357,0.8250,0.0053,0.0012</t>
-  </si>
-  <si>
-    <t>0.2897,0.8154,0.0015,0.0008</t>
-  </si>
-  <si>
-    <t>0.1547,0.8861,0.0050,0.0012</t>
-  </si>
-  <si>
-    <t>0.9441,0.0856,0.0029,0.0012</t>
-  </si>
-  <si>
-    <t>0.3947,0.7506,0.0013,0.0009</t>
-  </si>
-  <si>
-    <t>0.3858,0.3854,0.2842,0.0142</t>
-  </si>
-  <si>
-    <t>0.7590,0.0314,0.2178,0.0048</t>
-  </si>
-  <si>
-    <t>0.6335,0.0270,0.2542,0.0755</t>
-  </si>
-  <si>
-    <t>0.7252,0.0187,0.2732,0.0155</t>
-  </si>
-  <si>
-    <t>0.7773,0.0356,0.1376,0.0302</t>
-  </si>
-  <si>
-    <t>0.0491,0.0169,0.9373,0.0136</t>
-  </si>
-  <si>
-    <t>0.1074,0.2675,0.7445,0.0349</t>
-  </si>
-  <si>
-    <t>0.0725,0.0671,0.8972,0.0142</t>
-  </si>
-  <si>
-    <t>0.0406,0.0697,0.9234,0.0124</t>
-  </si>
-  <si>
-    <t>0.0181,0.7169,0.4901,0.0150</t>
-  </si>
-  <si>
-    <t>0.9923,0.0013,0.0001,0.0019</t>
-  </si>
-  <si>
-    <t>0.9723,0.0368,0.0010,0.0011</t>
-  </si>
-  <si>
-    <t>0.9832,0.0118,0.0003,0.0014</t>
-  </si>
-  <si>
-    <t>0.9942,0.0037,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9716,0.0248,0.0038,0.0020</t>
-  </si>
-  <si>
-    <t>0.9839,0.0199,0.0012,0.0007</t>
-  </si>
-  <si>
-    <t>0.9875,0.0028,0.0004,0.0035</t>
-  </si>
-  <si>
-    <t>0.9867,0.0071,0.0015,0.0015</t>
-  </si>
-  <si>
-    <t>0.1074,0.0771,0.8718,0.0161</t>
-  </si>
-  <si>
-    <t>0.0436,0.9103,0.0111,0.0351</t>
-  </si>
-  <si>
-    <t>0.9048,0.0255,0.0284,0.0223</t>
-  </si>
-  <si>
-    <t>0.0038,0.0213,0.9837,0.0056</t>
-  </si>
-  <si>
-    <t>0.0025,0.0280,0.9918,0.0010</t>
-  </si>
-  <si>
-    <t>0.0042,0.0133,0.9834,0.0037</t>
-  </si>
-  <si>
-    <t>0.0008,0.0010,0.9967,0.0017</t>
-  </si>
-  <si>
-    <t>0.1499,0.0146,0.8658,0.0084</t>
-  </si>
-  <si>
-    <t>0.0016,0.0148,0.9960,0.0004</t>
-  </si>
-  <si>
-    <t>0.0283,0.0734,0.9327,0.0121</t>
-  </si>
-  <si>
-    <t>0.2713,0.1510,0.6566,0.0188</t>
-  </si>
-  <si>
-    <t>0.5088,0.0087,0.5119,0.0187</t>
-  </si>
-  <si>
-    <t>0.7666,0.0365,0.2109,0.0153</t>
-  </si>
-  <si>
-    <t>0.7709,0.0474,0.0969,0.0754</t>
-  </si>
-  <si>
-    <t>0.9882,0.0080,0.0008,0.0010</t>
-  </si>
-  <si>
-    <t>0.9890,0.0032,0.0005,0.0021</t>
-  </si>
-  <si>
-    <t>0.9954,0.0015,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9863,0.0134,0.0008,0.0007</t>
-  </si>
-  <si>
-    <t>0.9885,0.0067,0.0004,0.0013</t>
-  </si>
-  <si>
-    <t>0.9814,0.0221,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.9928,0.0022,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9810,0.0264,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.0327,0.0870,0.9373,0.0022</t>
-  </si>
-  <si>
-    <t>0.0097,0.0341,0.9752,0.0049</t>
-  </si>
-  <si>
-    <t>0.0391,0.0296,0.9427,0.0075</t>
-  </si>
-  <si>
-    <t>0.0073,0.5194,0.8047,0.0014</t>
-  </si>
-  <si>
-    <t>0.0478,0.0071,0.9587,0.0026</t>
-  </si>
-  <si>
-    <t>0.3004,0.0415,0.1350,0.6381</t>
-  </si>
-  <si>
-    <t>0.1076,0.0058,0.7628,0.1338</t>
-  </si>
-  <si>
-    <t>0.0240,0.1777,0.9365,0.0059</t>
-  </si>
-  <si>
-    <t>0.4606,0.0027,0.0023,0.7686</t>
-  </si>
-  <si>
-    <t>0.0776,0.1673,0.0023,0.9301</t>
-  </si>
-  <si>
-    <t>0.1562,0.0586,0.0034,0.8985</t>
-  </si>
-  <si>
-    <t>0.0030,0.0004,0.0011,0.9977</t>
-  </si>
-  <si>
-    <t>0.0014,0.0006,0.0004,0.9989</t>
-  </si>
-  <si>
-    <t>0.8530,0.0076,0.0841,0.0290</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.8941,0.0192,0.0220,0.0444</t>
+  </si>
+  <si>
+    <t>0.0085,0.0065,0.0020,0.9929</t>
+  </si>
+  <si>
+    <t>0.8753,0.0340,0.0147,0.0443</t>
+  </si>
+  <si>
+    <t>0.2007,0.0048,0.0036,0.9150</t>
+  </si>
+  <si>
+    <t>0.9961,0.0023,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9931,0.0012,0.0002,0.0020</t>
+  </si>
+  <si>
+    <t>0.9930,0.0029,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9930,0.0022,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.9835,0.0197,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.9947,0.0029,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9965,0.0004,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9936,0.0041,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.6590,0.1371,0.2268,0.0077</t>
+  </si>
+  <si>
+    <t>0.3131,0.0300,0.7583,0.0033</t>
+  </si>
+  <si>
+    <t>0.5025,0.0096,0.6604,0.0015</t>
+  </si>
+  <si>
+    <t>0.1760,0.0686,0.7756,0.0126</t>
+  </si>
+  <si>
+    <t>0.6797,0.0973,0.2758,0.0374</t>
+  </si>
+  <si>
+    <t>0.0048,0.9914,0.0046,0.0003</t>
+  </si>
+  <si>
+    <t>0.0033,0.9944,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0612,0.9448,0.0065,0.0011</t>
+  </si>
+  <si>
+    <t>0.0091,0.9891,0.0030,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.9982,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.7043,0.0647,0.2642,0.0221</t>
+  </si>
+  <si>
+    <t>0.6303,0.0046,0.5166,0.0028</t>
+  </si>
+  <si>
+    <t>0.0450,0.0070,0.9409,0.0160</t>
+  </si>
+  <si>
+    <t>0.0449,0.0224,0.9300,0.0085</t>
+  </si>
+  <si>
+    <t>0.1610,0.0025,0.8868,0.0058</t>
+  </si>
+  <si>
+    <t>0.3129,0.0060,0.7319,0.0157</t>
+  </si>
+  <si>
+    <t>0.0134,0.0026,0.9833,0.0034</t>
+  </si>
+  <si>
+    <t>0.6456,0.4008,0.0368,0.0018</t>
+  </si>
+  <si>
+    <t>0.4421,0.4111,0.2569,0.0194</t>
+  </si>
+  <si>
+    <t>0.0012,0.0056,0.9917,0.0119</t>
+  </si>
+  <si>
+    <t>0.0079,0.9708,0.0504,0.0018</t>
+  </si>
+  <si>
+    <t>0.7442,0.3121,0.0240,0.0078</t>
+  </si>
+  <si>
+    <t>0.7048,0.1515,0.1815,0.0205</t>
+  </si>
+  <si>
+    <t>0.7094,0.4400,0.0054,0.0007</t>
+  </si>
+  <si>
+    <t>0.0315,0.9067,0.2092,0.0058</t>
+  </si>
+  <si>
+    <t>0.0135,0.9168,0.1933,0.0322</t>
+  </si>
+  <si>
+    <t>0.0698,0.1505,0.8666,0.0209</t>
+  </si>
+  <si>
+    <t>0.3028,0.0529,0.6907,0.0094</t>
+  </si>
+  <si>
+    <t>0.0503,0.0051,0.7684,0.1555</t>
+  </si>
+  <si>
+    <t>0.0318,0.1417,0.9259,0.0018</t>
+  </si>
+  <si>
+    <t>0.0201,0.9505,0.0508,0.0044</t>
+  </si>
+  <si>
+    <t>0.1050,0.0168,0.9094,0.0043</t>
+  </si>
+  <si>
+    <t>0.0440,0.8435,0.0133,0.5200</t>
+  </si>
+  <si>
+    <t>0.0009,0.9932,0.0025,0.0018</t>
+  </si>
+  <si>
+    <t>0.0265,0.9528,0.0258,0.0012</t>
+  </si>
+  <si>
+    <t>0.0193,0.9619,0.0079,0.0005</t>
+  </si>
+  <si>
+    <t>0.0201,0.0801,0.9365,0.0094</t>
+  </si>
+  <si>
+    <t>0.0217,0.4346,0.8467,0.0019</t>
+  </si>
+  <si>
+    <t>0.1600,0.0152,0.8386,0.0176</t>
+  </si>
+  <si>
+    <t>0.1185,0.0067,0.9120,0.0035</t>
+  </si>
+  <si>
+    <t>0.0165,0.0200,0.9638,0.0169</t>
+  </si>
+  <si>
+    <t>0.0148,0.0074,0.9772,0.0032</t>
+  </si>
+  <si>
+    <t>0.9821,0.0131,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.9727,0.0263,0.0012,0.0015</t>
+  </si>
+  <si>
+    <t>0.9816,0.0082,0.0020,0.0030</t>
+  </si>
+  <si>
+    <t>0.0023,0.0154,0.9921,0.0035</t>
+  </si>
+  <si>
+    <t>0.9889,0.0052,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.9845,0.0072,0.0012,0.0019</t>
+  </si>
+  <si>
+    <t>0.9577,0.0554,0.0055,0.0014</t>
+  </si>
+  <si>
+    <t>0.0041,0.9287,0.7555,0.0007</t>
+  </si>
+  <si>
+    <t>0.0205,0.0222,0.9545,0.0069</t>
+  </si>
+  <si>
+    <t>0.0151,0.0852,0.9448,0.0192</t>
+  </si>
+  <si>
+    <t>0.0005,0.8027,0.9866,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.0058,0.9952,0.0007</t>
+  </si>
+  <si>
+    <t>0.0018,0.9926,0.0268,0.0002</t>
+  </si>
+  <si>
+    <t>0.0045,0.9898,0.0027,0.0004</t>
+  </si>
+  <si>
+    <t>0.8306,0.0112,0.2035,0.0052</t>
+  </si>
+  <si>
+    <t>0.4907,0.1699,0.4484,0.0159</t>
+  </si>
+  <si>
+    <t>0.0098,0.0137,0.9847,0.0011</t>
+  </si>
+  <si>
+    <t>0.0057,0.8923,0.5126,0.0005</t>
+  </si>
+  <si>
+    <t>0.0172,0.8139,0.7091,0.0016</t>
+  </si>
+  <si>
+    <t>0.0034,0.9845,0.0402,0.0008</t>
+  </si>
+  <si>
+    <t>0.0023,0.8877,0.8380,0.0012</t>
+  </si>
+  <si>
+    <t>0.0799,0.0042,0.0155,0.9360</t>
+  </si>
+  <si>
+    <t>0.0005,0.0007,0.0012,0.9991</t>
+  </si>
+  <si>
+    <t>0.0006,0.0005,0.0005,0.9991</t>
+  </si>
+  <si>
+    <t>0.0018,0.0012,0.0032,0.9970</t>
+  </si>
+  <si>
+    <t>0.0042,0.0014,0.0007,0.9970</t>
+  </si>
+  <si>
+    <t>0.0019,0.0090,0.0011,0.9972</t>
+  </si>
+  <si>
+    <t>0.0017,0.9422,0.8048,0.0003</t>
+  </si>
+  <si>
+    <t>0.0089,0.7906,0.8270,0.0008</t>
+  </si>
+  <si>
+    <t>0.0113,0.8836,0.4096,0.0009</t>
+  </si>
+  <si>
+    <t>0.0047,0.4269,0.9519,0.0007</t>
+  </si>
+  <si>
+    <t>0.0011,0.9687,0.6618,0.0001</t>
+  </si>
+  <si>
+    <t>0.0039,0.9564,0.3297,0.0006</t>
+  </si>
+  <si>
+    <t>0.9936,0.0032,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.9857,0.0129,0.0012,0.0008</t>
+  </si>
+  <si>
+    <t>0.9739,0.0396,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9926,0.0049,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9846,0.0142,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9887,0.0017,0.0001,0.0027</t>
+  </si>
+  <si>
+    <t>0.9906,0.0039,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9574,0.0666,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.9953,0.0009,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9959,0.0011,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9954,0.0026,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9971,0.0011,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9895,0.0032,0.0006,0.0014</t>
+  </si>
+  <si>
+    <t>0.9909,0.0024,0.0006,0.0021</t>
+  </si>
+  <si>
+    <t>0.9927,0.0005,0.0001,0.0033</t>
+  </si>
+  <si>
+    <t>0.9976,0.0006,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0057,0.0023,0.9899,0.0027</t>
+  </si>
+  <si>
+    <t>0.0268,0.0137,0.9479,0.0235</t>
+  </si>
+  <si>
+    <t>0.6623,0.1460,0.1961,0.1016</t>
+  </si>
+  <si>
+    <t>0.2786,0.0106,0.7752,0.0151</t>
+  </si>
+  <si>
+    <t>0.0280,0.9719,0.0024,0.0004</t>
+  </si>
+  <si>
+    <t>0.0220,0.9765,0.0030,0.0003</t>
+  </si>
+  <si>
+    <t>0.0046,0.9905,0.0007,0.0011</t>
+  </si>
+  <si>
+    <t>0.0589,0.9357,0.0068,0.0026</t>
+  </si>
+  <si>
+    <t>0.0911,0.9286,0.0044,0.0004</t>
+  </si>
+  <si>
+    <t>0.0036,0.9913,0.0032,0.0006</t>
+  </si>
+  <si>
+    <t>0.8422,0.2351,0.0063,0.0041</t>
+  </si>
+  <si>
+    <t>0.5253,0.3969,0.1179,0.0673</t>
+  </si>
+  <si>
+    <t>0.7711,0.0325,0.1875,0.0248</t>
+  </si>
+  <si>
+    <t>0.5505,0.2595,0.0555,0.1037</t>
+  </si>
+  <si>
+    <t>0.4967,0.0657,0.4877,0.0409</t>
+  </si>
+  <si>
+    <t>0.0222,0.4338,0.0015,0.7965</t>
+  </si>
+  <si>
+    <t>0.0017,0.9923,0.0038,0.0009</t>
+  </si>
+  <si>
+    <t>0.0006,0.9929,0.0034,0.0021</t>
+  </si>
+  <si>
+    <t>0.0416,0.9395,0.0248,0.0076</t>
+  </si>
+  <si>
+    <t>0.0002,0.9822,0.8294,0.0001</t>
+  </si>
+  <si>
+    <t>0.0051,0.9804,0.1247,0.0004</t>
+  </si>
+  <si>
+    <t>0.8522,0.2359,0.0069,0.0010</t>
+  </si>
+  <si>
+    <t>0.6685,0.4552,0.0071,0.0014</t>
+  </si>
+  <si>
+    <t>0.9920,0.0049,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9735,0.0098,0.0025,0.0067</t>
+  </si>
+  <si>
+    <t>0.9773,0.0187,0.0018,0.0019</t>
+  </si>
+  <si>
+    <t>0.9676,0.0110,0.0012,0.0054</t>
+  </si>
+  <si>
+    <t>0.9874,0.0063,0.0013,0.0016</t>
+  </si>
+  <si>
+    <t>0.9796,0.0170,0.0036,0.0013</t>
+  </si>
+  <si>
+    <t>0.9928,0.0004,0.0002,0.0035</t>
+  </si>
+  <si>
+    <t>0.9813,0.0090,0.0027,0.0019</t>
+  </si>
+  <si>
+    <t>0.0030,0.6314,0.9181,0.0012</t>
+  </si>
+  <si>
+    <t>0.0094,0.6691,0.8035,0.0009</t>
+  </si>
+  <si>
+    <t>0.0173,0.6351,0.7341,0.0052</t>
+  </si>
+  <si>
+    <t>0.0216,0.2373,0.8951,0.0008</t>
+  </si>
+  <si>
+    <t>0.7219,0.1290,0.0191,0.0928</t>
+  </si>
+  <si>
+    <t>0.7291,0.0656,0.2258,0.0174</t>
+  </si>
+  <si>
+    <t>0.2663,0.0131,0.7837,0.0090</t>
+  </si>
+  <si>
+    <t>0.7179,0.2419,0.0776,0.0160</t>
+  </si>
+  <si>
+    <t>0.0072,0.0029,0.0067,0.9914</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.0082,0.9977</t>
+  </si>
+  <si>
+    <t>0.0016,0.0120,0.0011,0.9974</t>
+  </si>
+  <si>
+    <t>0.0247,0.0068,0.0038,0.9841</t>
+  </si>
+  <si>
+    <t>0.0010,0.9392,0.7968,0.0003</t>
+  </si>
+  <si>
+    <t>0.9553,0.0355,0.0064,0.0031</t>
+  </si>
+  <si>
+    <t>0.6110,0.4789,0.0079,0.0051</t>
+  </si>
+  <si>
+    <t>0.9516,0.0006,0.0000,0.0532</t>
+  </si>
+  <si>
+    <t>0.2842,0.7970,0.0035,0.0014</t>
+  </si>
+  <si>
+    <t>0.9849,0.0030,0.0027,0.0031</t>
+  </si>
+  <si>
+    <t>0.4488,0.0130,0.0162,0.6108</t>
+  </si>
+  <si>
+    <t>0.9495,0.0063,0.0008,0.0243</t>
+  </si>
+  <si>
+    <t>0.0065,0.0381,0.9558,0.0297</t>
+  </si>
+  <si>
+    <t>0.8776,0.0017,0.0045,0.1242</t>
+  </si>
+  <si>
+    <t>0.9049,0.0048,0.0083,0.0621</t>
+  </si>
+  <si>
+    <t>0.0906,0.8985,0.0328,0.0029</t>
+  </si>
+  <si>
+    <t>0.9437,0.0377,0.0101,0.0036</t>
+  </si>
+  <si>
+    <t>0.8919,0.0678,0.0285,0.0071</t>
+  </si>
+  <si>
+    <t>0.0193,0.9459,0.0056,0.0285</t>
+  </si>
+  <si>
+    <t>0.8664,0.0814,0.0421,0.0014</t>
+  </si>
+  <si>
+    <t>0.6827,0.3638,0.0424,0.0047</t>
+  </si>
+  <si>
+    <t>0.9911,0.0026,0.0005,0.0013</t>
+  </si>
+  <si>
+    <t>0.9844,0.0056,0.0013,0.0032</t>
+  </si>
+  <si>
+    <t>0.9943,0.0014,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9846,0.0022,0.0011,0.0048</t>
+  </si>
+  <si>
+    <t>0.9887,0.0024,0.0007,0.0027</t>
+  </si>
+  <si>
+    <t>0.9725,0.0150,0.0010,0.0027</t>
+  </si>
+  <si>
+    <t>0.9851,0.0025,0.0004,0.0045</t>
+  </si>
+  <si>
+    <t>0.9774,0.0151,0.0012,0.0022</t>
+  </si>
+  <si>
+    <t>0.6757,0.4489,0.0047,0.0010</t>
+  </si>
+  <si>
+    <t>0.3570,0.7844,0.0018,0.0002</t>
+  </si>
+  <si>
+    <t>0.5463,0.5789,0.0070,0.0018</t>
+  </si>
+  <si>
+    <t>0.8742,0.1070,0.0180,0.0210</t>
+  </si>
+  <si>
+    <t>0.8619,0.1969,0.0051,0.0029</t>
+  </si>
+  <si>
+    <t>0.9700,0.0243,0.0027,0.0025</t>
+  </si>
+  <si>
+    <t>0.9647,0.0209,0.0084,0.0027</t>
+  </si>
+  <si>
+    <t>0.3380,0.7427,0.0059,0.0028</t>
+  </si>
+  <si>
+    <t>0.0192,0.0133,0.9851,0.0006</t>
+  </si>
+  <si>
+    <t>0.9375,0.0631,0.0083,0.0041</t>
+  </si>
+  <si>
+    <t>0.0033,0.0265,0.9887,0.0011</t>
+  </si>
+  <si>
+    <t>0.0081,0.0258,0.9586,0.0227</t>
+  </si>
+  <si>
+    <t>0.0837,0.0271,0.8938,0.0053</t>
+  </si>
+  <si>
+    <t>0.0379,0.1546,0.9092,0.0056</t>
+  </si>
+  <si>
+    <t>0.0182,0.0355,0.9541,0.0014</t>
+  </si>
+  <si>
+    <t>0.0106,0.0036,0.9894,0.0004</t>
+  </si>
+  <si>
+    <t>0.0590,0.0485,0.9214,0.0067</t>
+  </si>
+  <si>
+    <t>0.4059,0.0391,0.6341,0.0148</t>
+  </si>
+  <si>
+    <t>0.0379,0.0243,0.9560,0.0046</t>
+  </si>
+  <si>
+    <t>0.3678,0.0770,0.6092,0.0061</t>
+  </si>
+  <si>
+    <t>0.4927,0.4503,0.1105,0.0104</t>
+  </si>
+  <si>
+    <t>0.2683,0.4609,0.2684,0.0059</t>
+  </si>
+  <si>
+    <t>0.4934,0.2270,0.2218,0.0062</t>
+  </si>
+  <si>
+    <t>0.5629,0.0970,0.4137,0.0619</t>
+  </si>
+  <si>
+    <t>0.3406,0.3910,0.3207,0.0387</t>
+  </si>
+  <si>
+    <t>0.4729,0.6721,0.0044,0.0007</t>
+  </si>
+  <si>
+    <t>0.2110,0.8634,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9651,0.0483,0.0017,0.0011</t>
+  </si>
+  <si>
+    <t>0.8496,0.2647,0.0033,0.0018</t>
+  </si>
+  <si>
+    <t>0.8621,0.2623,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.6061,0.0950,0.2967,0.1105</t>
+  </si>
+  <si>
+    <t>0.6948,0.1755,0.1294,0.0384</t>
+  </si>
+  <si>
+    <t>0.8856,0.0135,0.0596,0.0155</t>
+  </si>
+  <si>
+    <t>0.8239,0.0396,0.1409,0.0058</t>
+  </si>
+  <si>
+    <t>0.8024,0.0637,0.1054,0.0281</t>
+  </si>
+  <si>
+    <t>0.0205,0.0087,0.9415,0.0720</t>
+  </si>
+  <si>
+    <t>0.0096,0.0462,0.9511,0.0304</t>
+  </si>
+  <si>
+    <t>0.0344,0.1264,0.9204,0.0084</t>
+  </si>
+  <si>
+    <t>0.0246,0.0341,0.9424,0.0121</t>
+  </si>
+  <si>
+    <t>0.0085,0.2277,0.9366,0.0023</t>
+  </si>
+  <si>
+    <t>0.9883,0.0059,0.0003,0.0015</t>
+  </si>
+  <si>
+    <t>0.9945,0.0008,0.0001,0.0016</t>
+  </si>
+  <si>
+    <t>0.9745,0.0337,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9866,0.0075,0.0020,0.0014</t>
+  </si>
+  <si>
+    <t>0.9913,0.0087,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9816,0.0116,0.0005,0.0022</t>
+  </si>
+  <si>
+    <t>0.9866,0.0071,0.0019,0.0013</t>
+  </si>
+  <si>
+    <t>0.9914,0.0023,0.0004,0.0017</t>
+  </si>
+  <si>
+    <t>0.0778,0.0126,0.9210,0.0107</t>
+  </si>
+  <si>
+    <t>0.5538,0.3838,0.1457,0.0124</t>
+  </si>
+  <si>
+    <t>0.9355,0.0095,0.0291,0.0113</t>
+  </si>
+  <si>
+    <t>0.0148,0.0249,0.9770,0.0019</t>
+  </si>
+  <si>
+    <t>0.0004,0.0299,0.9927,0.0017</t>
+  </si>
+  <si>
+    <t>0.0606,0.2195,0.8207,0.0081</t>
+  </si>
+  <si>
+    <t>0.0042,0.0026,0.9912,0.0043</t>
+  </si>
+  <si>
+    <t>0.1470,0.0196,0.8772,0.0061</t>
+  </si>
+  <si>
+    <t>0.0060,0.0090,0.9862,0.0070</t>
+  </si>
+  <si>
+    <t>0.0746,0.0145,0.9263,0.0049</t>
+  </si>
+  <si>
+    <t>0.1099,0.1457,0.8385,0.0125</t>
+  </si>
+  <si>
+    <t>0.6287,0.0197,0.4305,0.0058</t>
+  </si>
+  <si>
+    <t>0.5938,0.0092,0.4408,0.0134</t>
+  </si>
+  <si>
+    <t>0.8662,0.0072,0.0547,0.0242</t>
+  </si>
+  <si>
+    <t>0.9839,0.0122,0.0013,0.0017</t>
+  </si>
+  <si>
+    <t>0.9903,0.0103,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9928,0.0108,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9870,0.0116,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.9871,0.0039,0.0008,0.0024</t>
+  </si>
+  <si>
+    <t>0.9869,0.0173,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9917,0.0022,0.0003,0.0017</t>
+  </si>
+  <si>
+    <t>0.9883,0.0036,0.0002,0.0023</t>
+  </si>
+  <si>
+    <t>0.1115,0.1329,0.7644,0.0050</t>
+  </si>
+  <si>
+    <t>0.0103,0.5587,0.8452,0.0043</t>
+  </si>
+  <si>
+    <t>0.0173,0.0584,0.9594,0.0041</t>
+  </si>
+  <si>
+    <t>0.0902,0.5276,0.5348,0.0115</t>
+  </si>
+  <si>
+    <t>0.0963,0.0342,0.8968,0.0069</t>
+  </si>
+  <si>
+    <t>0.3359,0.0204,0.1113,0.6041</t>
+  </si>
+  <si>
+    <t>0.1711,0.0350,0.7980,0.0379</t>
+  </si>
+  <si>
+    <t>0.0381,0.0367,0.9185,0.0188</t>
+  </si>
+  <si>
+    <t>0.5863,0.0015,0.0017,0.6191</t>
+  </si>
+  <si>
+    <t>0.0117,0.2683,0.0016,0.9752</t>
+  </si>
+  <si>
+    <t>0.0222,0.0021,0.0014,0.9914</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.0046,0.9986</t>
+  </si>
+  <si>
+    <t>0.0009,0.0005,0.0001,0.9995</t>
+  </si>
+  <si>
+    <t>0.8629,0.0568,0.0085,0.0295</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1971,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1985,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1999,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2013,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2027,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2041,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2055,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2069,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2083,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2097,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2111,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2125,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2139,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2153,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2164,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2181,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2195,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2209,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2223,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2237,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2251,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2265,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2279,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2290,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2307,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2321,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2335,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2349,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2363,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2377,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2388,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2405,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2419,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2433,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2447,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2458,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2475,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2489,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2503,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2517,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2531,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2545,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2559,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2573,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2584,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2601,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2615,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2629,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2643,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,10 +2654,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2671,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2685,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2699,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2713,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2727,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2741,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2755,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2769,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2783,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2797,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2811,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2825,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2839,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2853,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2867,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2881,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2895,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2909,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2920,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2934,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2951,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2962,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2976,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2993,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3007,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3021,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3035,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3049,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3063,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3077,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3091,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3105,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3119,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3130,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3144,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3161,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3172,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3189,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3203,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3217,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3231,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3245,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3259,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3273,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3287,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3301,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3315,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3329,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3343,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3357,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3371,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3385,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3399,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3413,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3427,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3441,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3455,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3469,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3483,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3497,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3511,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3525,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3539,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3550,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3567,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3578,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3595,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3606,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3623,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3637,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3651,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3665,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3679,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3693,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3704,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3721,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3735,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3749,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3763,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3777,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3791,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3805,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3819,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3833,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3844,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3861,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3875,7 @@
         <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3889,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3903,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3917,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3928,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3945,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3959,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3973,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3987,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +4001,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4015,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4029,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4043,7 @@
         <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4057,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4068,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4085,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4096,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4113,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4127,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4141,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4155,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4169,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4183,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4197,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4211,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,10 +4222,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4239,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4253,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4267,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4281,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4295,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4309,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4323,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4337,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4351,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4362,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4379,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4390,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4407,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4403,10 +4418,10 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4435,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4449,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4463,7 @@
         <v>262</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4477,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4491,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4505,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4519,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4533,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4547,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4561,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4575,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4589,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4600,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4614,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4628,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4642,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4656,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4670,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4687,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4698,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4715,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4729,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,10 +4740,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4757,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4768,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4785,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4799,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4813,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4827,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4841,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4855,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4869,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4883,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4897,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4908,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4925,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4939,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4953,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4967,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4981,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4995,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5009,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5023,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5037,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5048,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5065,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5079,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5093,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5107,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5121,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5135,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5149,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5163,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5177,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5188,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5205,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5219,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5233,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5247,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5261,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5275,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5289,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5303,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5317,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5331,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5345,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,10 +5356,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5373,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5387,7 @@
         <v>263</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5401,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5415,7 @@
         <v>260</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5429,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5443,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5454,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5471,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5485,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5499,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5513,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5527,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
